--- a/data/trans_bre/IP1012-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Edad-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,0</t>
+          <t>-3,87; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,24</t>
+          <t>-1,91; 0,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,45</t>
+          <t>-2,29; 0,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,26; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,0</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,35</t>
+          <t>-0,81; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,05</t>
+          <t>-2,09; 1,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,0</t>
+          <t>-1,75; 1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,08</t>
+          <t>-1,24; 0,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,3</t>
+          <t>-1,14; 0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; -0,1</t>
+          <t>-0,9; -0,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-95,14; 91,75</t>
+          <t>-100,0; 51,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-88,09; 86,86</t>
+          <t>-89,2; 118,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1012-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Edad-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,0</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,25</t>
+          <t>-1,83; 0,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,28</t>
+          <t>-2,04; 0,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,0</t>
+          <t>-1,36; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,98</t>
+          <t>-0,81; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,08</t>
+          <t>-2,28; 0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,94</t>
+          <t>-1,82; 1,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,07</t>
+          <t>-1,19; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,29</t>
+          <t>-1,03; 0,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; -0,09</t>
+          <t>-0,99; -0,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,8</t>
+          <t>-100,0; 63,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-89,2; 118,29</t>
+          <t>-84,71; 142,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1012-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Edad-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,0</t>
+          <t>-3,78; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,25</t>
+          <t>-1,88; 0,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,46</t>
+          <t>-2,28; 0,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-3,17; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,99</t>
+          <t>-0,81; 2,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-1,77; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,86</t>
+          <t>-2,34; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,9</t>
+          <t>-1,68; 2,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,96; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,11</t>
+          <t>-1,21; 0,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,36</t>
+          <t>-1,07; 0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; -0,1</t>
+          <t>-0,89; -0,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,02</t>
+          <t>-95,14; 91,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,71; 142,48</t>
+          <t>-88,09; 86,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1012-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1012-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,127 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.003936939404032</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-3.775696763117516</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-68,6%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-63,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 0,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,25; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5468274970388842</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.4875244696891998</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2502258383933064</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6860416617204692</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.6354234090195835</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>47,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.875701673168829</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.281601475885353</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.249286182611511</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,17; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 2,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2440849861480118</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4530904382344061</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +731,215 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-38,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9136121577443479</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1916029274338176</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3276649681587867</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.4794916883438829</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 1,05</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,68; 2,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.16860860359825</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.8060600961018756</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.77367145451467</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.353566169384101</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.4435403024777667</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1088543386503752</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.8458487874572549</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3849756107007082</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1003560375494233</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.9999905896779238</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.343690274433989</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.682440174899727</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.95513522019717</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.046240916209975</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.003803809986078</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.859119550476109e-06</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-62,53%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-43,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,21; 0,08</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,07; 0,3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; -0,1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-95,14; 91,75</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-88,09; 86,86</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.4922561110353879</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.351981414056019</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3672980906298767</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.6252839396951515</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.4341398579368338</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.9999946681400167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.210957903549241</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.071430123225081</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.8891383266096509</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.9513574859094424</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8808707402600782</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.08403763593811826</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.3022668175813617</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.09645201821328275</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.9174915039315865</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.868557476459516</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +948,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
